--- a/tables/table-2-baseline-model-results.xlsx
+++ b/tables/table-2-baseline-model-results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{3E4FD764-6F2E-4073-8E15-E7B2356EF5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68924438-ACF3-4A86-AED1-F0425B61ABB0}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{3E4FD764-6F2E-4073-8E15-E7B2356EF5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D399F1BC-1F02-4044-9B3F-26C3CCCBF606}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E0120D6-E0F4-4A0E-BE96-999DA8FCAB55}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1E0120D6-E0F4-4A0E-BE96-999DA8FCAB55}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
     <t>55 min 4 s</t>
   </si>
   <si>
-    <t>Table 3: Baseline Model Results</t>
+    <t>Table 2: Baseline Model Results</t>
   </si>
 </sst>
 </file>
@@ -173,19 +173,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -205,10 +205,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -246,7 +250,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -352,7 +356,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -494,7 +498,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -503,24 +507,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89C7855C-5A04-412E-AB0C-64E10BA97935}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="4" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" customWidth="1"/>
+    <col min="3" max="4" width="12.453125" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" spans="1:5" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -537,139 +541,139 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>91.16</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>89.2</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>92.8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>94.21</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>92</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>94.4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>96.49</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>96.4</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>96.4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>98.2</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>93.6</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>97.2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>97.58</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>96</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>98.4</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>98.59</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>96</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>98.8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>97.16</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>95.2</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>97.2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>97.34</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>96.8</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>97.6</v>
       </c>
     </row>
